--- a/WorkBot/refactor/data/orders/Webstaurant/Webstaurant_Bakery_2025-10-04.xlsx
+++ b/WorkBot/refactor/data/orders/Webstaurant/Webstaurant_Bakery_2025-10-04.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,6 +470,276 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>102708283</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Spice - Ginger (Ground)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>22.99</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>22.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>10201311</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Spice - Italian Seasoning</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>87.89</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>87.89</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>711RGRMCRK50</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Graham Cracker - Crumb</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>118.49</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>236.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>245885CB</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Box Cake - 8x8x5</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>34.81</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>69.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>245882WB</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Box Cake - 8x8x2.5 (window)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>68.60</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>137.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>588MILK632</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Urnex - Rinza</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>17.99</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>17.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>707U72SPRDBK</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Black Plastic Spreader 7.51"</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>18.49</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>36.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>760SOUP32PBL</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Lid - Soup (32oz)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>40.49</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>80.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>760SOUP32MB</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Container - Soup (32oz)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>62.99</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>125.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>656095131</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Container - Muffin (12 Pack)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>65.49</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>130.98</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
